--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:52:49+00:00</t>
+    <t>2026-04-30T09:56:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:56:18+00:00</t>
+    <t>2026-04-30T12:26:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:26:28+00:00</t>
+    <t>2026-04-30T12:40:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:40:02+00:00</t>
+    <t>2026-04-30T12:42:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:42:30+00:00</t>
+    <t>2026-04-30T12:46:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:46:16+00:00</t>
+    <t>2026-04-30T13:10:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:10:34+00:00</t>
+    <t>2026-04-30T13:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/nr-add-more-examples/ig/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:20:47+00:00</t>
+    <t>2026-04-30T13:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
